--- a/지출결의서_260824.xlsx
+++ b/지출결의서_260824.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\김세희\01_업무자료\경영지원업무\01_(비즈메카) 기안서 결제\지출결의서\260922_소마미술관 월주차 정기권\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Master\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="12090"/>
   </bookViews>
   <sheets>
     <sheet name="2026 지출결의서" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2026 지출결의서'!$A$1:$M$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2026 지출결의서'!$A$1:$N$76</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>사업소명</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -190,15 +190,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>배송비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>내 역</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>소 계</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -241,10 +233,6 @@
   <si>
     <t>올림픽공원 월주차 신청
 (29루0608 - 김인태 상무님 차량)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>법인 구분</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -275,6 +263,22 @@
       마) 비용: 180,000원
       바) 법인구분: GSI
   라. 총 금액 : 360,000원</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>부가세</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>소 계</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>배송비</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -500,7 +504,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -564,27 +568,63 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -603,40 +643,22 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -979,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:M76"/>
+  <dimension ref="B1:N76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
@@ -991,29 +1013,31 @@
     <col min="8" max="8" width="11.5" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="2.125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="9" style="1"/>
-    <col min="19" max="19" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="10.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.625" style="1" customWidth="1"/>
+    <col min="14" max="15" width="2.125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="9" style="1"/>
+    <col min="20" max="20" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-    </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+    </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1023,123 +1047,129 @@
       </c>
       <c r="K2" s="19"/>
       <c r="L2" s="19"/>
-    </row>
-    <row r="3" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="28" t="s">
+      <c r="M2" s="19"/>
+    </row>
+    <row r="3" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="23" t="s">
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="38"/>
+    </row>
+    <row r="5" spans="2:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="41" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="2:13" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="24"/>
-    </row>
-    <row r="5" spans="2:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="24"/>
-    </row>
-    <row r="6" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="23" t="s">
+      <c r="L5" s="26"/>
+      <c r="M5" s="38"/>
+    </row>
+    <row r="6" spans="2:14" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="25">
+      <c r="C6" s="26"/>
+      <c r="D6" s="39">
         <f ca="1">TODAY()</f>
         <v>46293</v>
       </c>
-      <c r="E6" s="25"/>
+      <c r="E6" s="39"/>
       <c r="F6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" s="26"/>
+      <c r="G6" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="J6" s="26" t="s">
+      <c r="J6" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="23" t="s">
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="2:14" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="32">
+      <c r="C7" s="26"/>
+      <c r="D7" s="44">
         <f ca="1">D6</f>
         <v>46293</v>
       </c>
-      <c r="E7" s="32"/>
+      <c r="E7" s="44"/>
       <c r="F7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="26"/>
+      <c r="G7" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="24"/>
       <c r="I7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="23" t="s">
+      <c r="J7" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="2:14" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="33" t="str">
+      <c r="E8" s="45" t="str">
         <f>NUMBERSTRING(I8, 1) &amp; "원 정"</f>
         <v>삼십육만원 정</v>
       </c>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
       <c r="I8" s="35">
         <f>I62</f>
         <v>360000</v>
@@ -1147,31 +1177,33 @@
       <c r="J8" s="35"/>
       <c r="K8" s="35"/>
       <c r="L8" s="35"/>
-    </row>
-    <row r="9" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-    </row>
-    <row r="10" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="35"/>
+    </row>
+    <row r="9" spans="2:14" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+    </row>
+    <row r="10" spans="2:14" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
       <c r="F10" s="6" t="s">
         <v>12</v>
       </c>
@@ -1185,25 +1217,28 @@
         <v>15</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="23"/>
-    </row>
-    <row r="11" spans="2:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="26"/>
+    </row>
+    <row r="11" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8">
         <f>IF(C11="","",ROW()-10)</f>
         <v>1</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="27"/>
       <c r="F11" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G11" s="20">
         <v>1</v>
@@ -1217,21 +1252,22 @@
       <c r="J11" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="15"/>
       <c r="L11" s="27"/>
-    </row>
-    <row r="12" spans="2:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="27"/>
+    </row>
+    <row r="12" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8">
         <f>IF(C12="","",ROW()-10)</f>
         <v>2</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
       <c r="F12" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G12" s="20">
         <v>1</v>
@@ -1245,26 +1281,27 @@
       <c r="J12" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="K12" s="27"/>
+      <c r="K12" s="15"/>
       <c r="L12" s="27"/>
-    </row>
-    <row r="13" spans="2:13" ht="54" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="27"/>
+    </row>
+    <row r="13" spans="2:14" ht="54" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="8">
         <v>2</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="27"/>
       <c r="F13" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>36</v>
@@ -1272,28 +1309,29 @@
       <c r="J13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="15"/>
+      <c r="L13" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="27"/>
-    </row>
-    <row r="14" spans="2:13" ht="49.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="27"/>
+    </row>
+    <row r="14" spans="2:14" ht="49.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="8">
         <v>3</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="27"/>
       <c r="F14" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>36</v>
@@ -1301,12 +1339,13 @@
       <c r="J14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="27" t="s">
+      <c r="K14" s="15"/>
+      <c r="L14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="27"/>
-    </row>
-    <row r="15" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="27"/>
+    </row>
+    <row r="15" spans="2:14" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="str">
         <f t="shared" ref="B15:B60" si="0">IF(C15="","",ROW()-10)</f>
         <v/>
@@ -1322,10 +1361,11 @@
         <v/>
       </c>
       <c r="J15" s="12"/>
-      <c r="K15" s="27"/>
+      <c r="K15" s="12"/>
       <c r="L15" s="27"/>
-    </row>
-    <row r="16" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="27"/>
+    </row>
+    <row r="16" spans="2:14" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1341,10 +1381,11 @@
         <v/>
       </c>
       <c r="J16" s="12"/>
-      <c r="K16" s="27"/>
+      <c r="K16" s="12"/>
       <c r="L16" s="27"/>
-    </row>
-    <row r="17" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="27"/>
+    </row>
+    <row r="17" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1360,10 +1401,11 @@
         <v/>
       </c>
       <c r="J17" s="12"/>
-      <c r="K17" s="27"/>
+      <c r="K17" s="12"/>
       <c r="L17" s="27"/>
-    </row>
-    <row r="18" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="27"/>
+    </row>
+    <row r="18" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1379,10 +1421,11 @@
         <v/>
       </c>
       <c r="J18" s="12"/>
-      <c r="K18" s="27"/>
+      <c r="K18" s="12"/>
       <c r="L18" s="27"/>
-    </row>
-    <row r="19" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="27"/>
+    </row>
+    <row r="19" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1398,10 +1441,11 @@
         <v/>
       </c>
       <c r="J19" s="12"/>
-      <c r="K19" s="27"/>
+      <c r="K19" s="12"/>
       <c r="L19" s="27"/>
-    </row>
-    <row r="20" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="27"/>
+    </row>
+    <row r="20" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1417,10 +1461,11 @@
         <v/>
       </c>
       <c r="J20" s="12"/>
-      <c r="K20" s="27"/>
+      <c r="K20" s="12"/>
       <c r="L20" s="27"/>
-    </row>
-    <row r="21" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M20" s="27"/>
+    </row>
+    <row r="21" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1436,10 +1481,11 @@
         <v/>
       </c>
       <c r="J21" s="12"/>
-      <c r="K21" s="27"/>
+      <c r="K21" s="12"/>
       <c r="L21" s="27"/>
-    </row>
-    <row r="22" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="27"/>
+    </row>
+    <row r="22" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1455,10 +1501,11 @@
         <v/>
       </c>
       <c r="J22" s="12"/>
-      <c r="K22" s="27"/>
+      <c r="K22" s="12"/>
       <c r="L22" s="27"/>
-    </row>
-    <row r="23" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="27"/>
+    </row>
+    <row r="23" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1474,10 +1521,11 @@
         <v/>
       </c>
       <c r="J23" s="12"/>
-      <c r="K23" s="27"/>
+      <c r="K23" s="12"/>
       <c r="L23" s="27"/>
-    </row>
-    <row r="24" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M23" s="27"/>
+    </row>
+    <row r="24" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1493,10 +1541,11 @@
         <v/>
       </c>
       <c r="J24" s="12"/>
-      <c r="K24" s="27"/>
+      <c r="K24" s="12"/>
       <c r="L24" s="27"/>
-    </row>
-    <row r="25" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M24" s="27"/>
+    </row>
+    <row r="25" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1512,10 +1561,11 @@
         <v/>
       </c>
       <c r="J25" s="12"/>
-      <c r="K25" s="27"/>
+      <c r="K25" s="12"/>
       <c r="L25" s="27"/>
-    </row>
-    <row r="26" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M25" s="27"/>
+    </row>
+    <row r="26" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1531,10 +1581,11 @@
         <v/>
       </c>
       <c r="J26" s="12"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-    </row>
-    <row r="27" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K26" s="12"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+    </row>
+    <row r="27" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1550,17 +1601,18 @@
         <v/>
       </c>
       <c r="J27" s="12"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-    </row>
-    <row r="28" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K27" s="12"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
+    </row>
+    <row r="28" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="9"/>
       <c r="G28" s="14"/>
       <c r="H28" s="11"/>
@@ -1569,17 +1621,18 @@
         <v/>
       </c>
       <c r="J28" s="12"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-    </row>
-    <row r="29" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="12"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+    </row>
+    <row r="29" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
       <c r="F29" s="9"/>
       <c r="G29" s="14"/>
       <c r="H29" s="11"/>
@@ -1588,17 +1641,18 @@
         <v/>
       </c>
       <c r="J29" s="12"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-    </row>
-    <row r="30" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="12"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+    </row>
+    <row r="30" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="9"/>
       <c r="G30" s="14"/>
       <c r="H30" s="11"/>
@@ -1607,17 +1661,18 @@
         <v/>
       </c>
       <c r="J30" s="12"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-    </row>
-    <row r="31" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K30" s="12"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
+    </row>
+    <row r="31" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
       <c r="F31" s="9"/>
       <c r="G31" s="14"/>
       <c r="H31" s="11"/>
@@ -1626,17 +1681,18 @@
         <v/>
       </c>
       <c r="J31" s="12"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-    </row>
-    <row r="32" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="12"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+    </row>
+    <row r="32" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="9"/>
       <c r="G32" s="14"/>
       <c r="H32" s="11"/>
@@ -1645,17 +1701,18 @@
         <v/>
       </c>
       <c r="J32" s="12"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-    </row>
-    <row r="33" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="12"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
+    </row>
+    <row r="33" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
       <c r="F33" s="9"/>
       <c r="G33" s="14"/>
       <c r="H33" s="11"/>
@@ -1664,17 +1721,18 @@
         <v/>
       </c>
       <c r="J33" s="12"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-    </row>
-    <row r="34" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="12"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+    </row>
+    <row r="34" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
       <c r="F34" s="9"/>
       <c r="G34" s="14"/>
       <c r="H34" s="11"/>
@@ -1683,17 +1741,18 @@
         <v/>
       </c>
       <c r="J34" s="12"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-    </row>
-    <row r="35" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K34" s="12"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+    </row>
+    <row r="35" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
       <c r="F35" s="9"/>
       <c r="G35" s="14"/>
       <c r="H35" s="11"/>
@@ -1702,17 +1761,18 @@
         <v/>
       </c>
       <c r="J35" s="12"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-    </row>
-    <row r="36" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K35" s="12"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+    </row>
+    <row r="36" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="9"/>
       <c r="G36" s="14"/>
       <c r="H36" s="11"/>
@@ -1721,17 +1781,18 @@
         <v/>
       </c>
       <c r="J36" s="12"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-    </row>
-    <row r="37" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K36" s="12"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+    </row>
+    <row r="37" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
       <c r="F37" s="9"/>
       <c r="G37" s="14"/>
       <c r="H37" s="11"/>
@@ -1740,17 +1801,18 @@
         <v/>
       </c>
       <c r="J37" s="12"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-    </row>
-    <row r="38" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K37" s="12"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+    </row>
+    <row r="38" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
       <c r="F38" s="9"/>
       <c r="G38" s="14"/>
       <c r="H38" s="11"/>
@@ -1759,17 +1821,18 @@
         <v/>
       </c>
       <c r="J38" s="12"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-    </row>
-    <row r="39" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K38" s="12"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+    </row>
+    <row r="39" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
       <c r="F39" s="9"/>
       <c r="G39" s="14"/>
       <c r="H39" s="11"/>
@@ -1778,17 +1841,18 @@
         <v/>
       </c>
       <c r="J39" s="12"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="26"/>
-    </row>
-    <row r="40" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K39" s="12"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+    </row>
+    <row r="40" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
       <c r="F40" s="9"/>
       <c r="G40" s="14"/>
       <c r="H40" s="11"/>
@@ -1797,17 +1861,18 @@
         <v/>
       </c>
       <c r="J40" s="12"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="26"/>
-    </row>
-    <row r="41" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K40" s="12"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+    </row>
+    <row r="41" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
       <c r="F41" s="9"/>
       <c r="G41" s="14"/>
       <c r="H41" s="11"/>
@@ -1816,17 +1881,18 @@
         <v/>
       </c>
       <c r="J41" s="12"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-    </row>
-    <row r="42" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K41" s="12"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+    </row>
+    <row r="42" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
       <c r="F42" s="9"/>
       <c r="G42" s="14"/>
       <c r="H42" s="11"/>
@@ -1835,17 +1901,18 @@
         <v/>
       </c>
       <c r="J42" s="12"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-    </row>
-    <row r="43" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K42" s="12"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+    </row>
+    <row r="43" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
       <c r="F43" s="9"/>
       <c r="G43" s="14"/>
       <c r="H43" s="11"/>
@@ -1854,17 +1921,18 @@
         <v/>
       </c>
       <c r="J43" s="12"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
-    </row>
-    <row r="44" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K43" s="12"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="24"/>
+    </row>
+    <row r="44" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="9"/>
       <c r="G44" s="14"/>
       <c r="H44" s="16"/>
@@ -1873,17 +1941,18 @@
         <v/>
       </c>
       <c r="J44" s="12"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-    </row>
-    <row r="45" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K44" s="12"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="24"/>
+    </row>
+    <row r="45" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
       <c r="F45" s="9"/>
       <c r="G45" s="14"/>
       <c r="H45" s="16"/>
@@ -1892,17 +1961,18 @@
         <v/>
       </c>
       <c r="J45" s="12"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-    </row>
-    <row r="46" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K45" s="12"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="24"/>
+    </row>
+    <row r="46" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
       <c r="F46" s="9"/>
       <c r="G46" s="14"/>
       <c r="H46" s="16"/>
@@ -1911,17 +1981,18 @@
         <v/>
       </c>
       <c r="J46" s="12"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-    </row>
-    <row r="47" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K46" s="12"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="24"/>
+    </row>
+    <row r="47" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
       <c r="F47" s="9"/>
       <c r="G47" s="14"/>
       <c r="H47" s="16"/>
@@ -1930,17 +2001,18 @@
         <v/>
       </c>
       <c r="J47" s="12"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-    </row>
-    <row r="48" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K47" s="12"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="24"/>
+    </row>
+    <row r="48" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
       <c r="F48" s="9"/>
       <c r="G48" s="14"/>
       <c r="H48" s="16"/>
@@ -1949,17 +2021,18 @@
         <v/>
       </c>
       <c r="J48" s="12"/>
-      <c r="K48" s="26"/>
-      <c r="L48" s="26"/>
-    </row>
-    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K48" s="12"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="24"/>
+    </row>
+    <row r="49" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
       <c r="F49" s="9"/>
       <c r="G49" s="14"/>
       <c r="H49" s="16"/>
@@ -1968,17 +2041,18 @@
         <v/>
       </c>
       <c r="J49" s="12"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-    </row>
-    <row r="50" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K49" s="12"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="24"/>
+    </row>
+    <row r="50" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
       <c r="F50" s="9"/>
       <c r="G50" s="14"/>
       <c r="H50" s="16"/>
@@ -1987,17 +2061,18 @@
         <v/>
       </c>
       <c r="J50" s="12"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
-    </row>
-    <row r="51" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K50" s="12"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="24"/>
+    </row>
+    <row r="51" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
       <c r="F51" s="9"/>
       <c r="G51" s="14"/>
       <c r="H51" s="16"/>
@@ -2006,17 +2081,18 @@
         <v/>
       </c>
       <c r="J51" s="12"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-    </row>
-    <row r="52" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K51" s="12"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
+    </row>
+    <row r="52" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
       <c r="F52" s="9"/>
       <c r="G52" s="14"/>
       <c r="H52" s="16"/>
@@ -2025,17 +2101,18 @@
         <v/>
       </c>
       <c r="J52" s="12"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="26"/>
-    </row>
-    <row r="53" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K52" s="12"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
+    </row>
+    <row r="53" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
       <c r="F53" s="9"/>
       <c r="G53" s="14"/>
       <c r="H53" s="16"/>
@@ -2044,17 +2121,18 @@
         <v/>
       </c>
       <c r="J53" s="12"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-    </row>
-    <row r="54" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K53" s="12"/>
+      <c r="L53" s="24"/>
+      <c r="M53" s="24"/>
+    </row>
+    <row r="54" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
       <c r="F54" s="9"/>
       <c r="G54" s="14"/>
       <c r="H54" s="16"/>
@@ -2063,17 +2141,18 @@
         <v/>
       </c>
       <c r="J54" s="12"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
-    </row>
-    <row r="55" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K54" s="12"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="24"/>
+    </row>
+    <row r="55" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
       <c r="F55" s="9"/>
       <c r="G55" s="14"/>
       <c r="H55" s="16"/>
@@ -2082,17 +2161,18 @@
         <v/>
       </c>
       <c r="J55" s="12"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-    </row>
-    <row r="56" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K55" s="12"/>
+      <c r="L55" s="24"/>
+      <c r="M55" s="24"/>
+    </row>
+    <row r="56" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
       <c r="F56" s="9"/>
       <c r="G56" s="14"/>
       <c r="H56" s="16"/>
@@ -2101,17 +2181,18 @@
         <v/>
       </c>
       <c r="J56" s="12"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
-    </row>
-    <row r="57" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K56" s="12"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="24"/>
+    </row>
+    <row r="57" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
       <c r="F57" s="9"/>
       <c r="G57" s="14"/>
       <c r="H57" s="16"/>
@@ -2120,17 +2201,18 @@
         <v/>
       </c>
       <c r="J57" s="12"/>
-      <c r="K57" s="26"/>
-      <c r="L57" s="26"/>
-    </row>
-    <row r="58" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K57" s="12"/>
+      <c r="L57" s="24"/>
+      <c r="M57" s="24"/>
+    </row>
+    <row r="58" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
       <c r="F58" s="9"/>
       <c r="G58" s="14"/>
       <c r="H58" s="16"/>
@@ -2139,17 +2221,18 @@
         <v/>
       </c>
       <c r="J58" s="12"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="26"/>
-    </row>
-    <row r="59" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K58" s="12"/>
+      <c r="L58" s="24"/>
+      <c r="M58" s="24"/>
+    </row>
+    <row r="59" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
       <c r="F59" s="9"/>
       <c r="G59" s="14"/>
       <c r="H59" s="16"/>
@@ -2158,17 +2241,18 @@
         <v/>
       </c>
       <c r="J59" s="12"/>
-      <c r="K59" s="26"/>
-      <c r="L59" s="26"/>
-    </row>
-    <row r="60" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K59" s="12"/>
+      <c r="L59" s="24"/>
+      <c r="M59" s="24"/>
+    </row>
+    <row r="60" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
       <c r="F60" s="9"/>
       <c r="G60" s="14"/>
       <c r="H60" s="16"/>
@@ -2177,74 +2261,78 @@
         <v/>
       </c>
       <c r="J60" s="12"/>
-      <c r="K60" s="26"/>
-      <c r="L60" s="26"/>
-    </row>
-    <row r="61" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23" t="s">
+      <c r="K60" s="12"/>
+      <c r="L60" s="24"/>
+      <c r="M60" s="24"/>
+    </row>
+    <row r="61" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="J61" s="23"/>
-      <c r="K61" s="27" t="s">
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
+      <c r="L61" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="L61" s="27"/>
-    </row>
-    <row r="62" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="23"/>
-      <c r="I62" s="38">
+      <c r="M61" s="27"/>
+    </row>
+    <row r="62" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="49">
         <f>SUM(H11:H14)</f>
         <v>360000</v>
       </c>
-      <c r="J62" s="38"/>
-      <c r="K62" s="27" t="s">
+      <c r="J62" s="50"/>
+      <c r="K62" s="51"/>
+      <c r="L62" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="L62" s="27"/>
-    </row>
-    <row r="63" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="23" t="s">
+      <c r="M62" s="27"/>
+    </row>
+    <row r="63" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="23"/>
-      <c r="D63" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="E63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E63" s="24"/>
       <c r="F63" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G63" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="26"/>
-      <c r="K63" s="26"/>
-      <c r="L63" s="26"/>
-    </row>
-    <row r="64" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="23" t="s">
+      <c r="G63" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
+      <c r="J63" s="24"/>
+      <c r="K63" s="24"/>
+      <c r="L63" s="24"/>
+      <c r="M63" s="24"/>
+    </row>
+    <row r="64" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C64" s="23"/>
+      <c r="C64" s="26"/>
       <c r="D64" s="6" t="s">
         <v>19</v>
       </c>
@@ -2252,31 +2340,33 @@
       <c r="F64" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="39"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
       <c r="J64" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K64" s="26"/>
-      <c r="L64" s="26"/>
-    </row>
-    <row r="65" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="23" t="s">
+      <c r="K64" s="21"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="24"/>
+    </row>
+    <row r="65" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="23"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="41"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="41"/>
-      <c r="J65" s="41"/>
-      <c r="K65" s="41"/>
-      <c r="L65" s="42"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C65" s="26"/>
+      <c r="D65" s="29"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
+      <c r="M65" s="31"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
@@ -2288,23 +2378,25 @@
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="43" t="s">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C67" s="43"/>
-      <c r="D67" s="43"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="43"/>
-      <c r="H67" s="43"/>
-      <c r="I67" s="43"/>
-      <c r="J67" s="43"/>
-      <c r="K67" s="43"/>
-      <c r="L67" s="43"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
@@ -2316,272 +2408,280 @@
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="43" t="s">
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C69" s="43"/>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="43"/>
-      <c r="H69" s="43"/>
-      <c r="I69" s="43"/>
-      <c r="J69" s="43"/>
-      <c r="K69" s="43"/>
-      <c r="L69" s="43"/>
-    </row>
-    <row r="70" spans="2:12" ht="303.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
-      <c r="J70" s="37"/>
-      <c r="K70" s="37"/>
-      <c r="L70" s="37"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-    </row>
-    <row r="72" spans="2:12" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="43" t="s">
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="32"/>
+      <c r="M69" s="32"/>
+    </row>
+    <row r="70" spans="2:13" ht="303.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="25"/>
+      <c r="K70" s="25"/>
+      <c r="L70" s="25"/>
+      <c r="M70" s="25"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
+      <c r="J71" s="36"/>
+      <c r="K71" s="36"/>
+      <c r="L71" s="36"/>
+      <c r="M71" s="36"/>
+    </row>
+    <row r="72" spans="2:13" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C72" s="43"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="43"/>
-      <c r="H72" s="43"/>
-      <c r="I72" s="43"/>
-      <c r="J72" s="43"/>
-      <c r="K72" s="43"/>
-      <c r="L72" s="43"/>
-    </row>
-    <row r="73" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="37"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B74" s="21"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B75" s="37" t="s">
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="32"/>
+      <c r="L72" s="32"/>
+      <c r="M72" s="32"/>
+    </row>
+    <row r="73" spans="2:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="25"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="25"/>
+      <c r="L73" s="25"/>
+      <c r="M73" s="25"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
+      <c r="L74" s="36"/>
+      <c r="M74" s="36"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B75" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
-      <c r="K75" s="37"/>
-      <c r="L75" s="37"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B76" s="22"/>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="22"/>
-      <c r="J76" s="22"/>
-      <c r="K76" s="22"/>
-      <c r="L76" s="22"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="25"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="25"/>
+      <c r="L75" s="25"/>
+      <c r="M75" s="25"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B76" s="37"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="H76" s="37"/>
+      <c r="I76" s="37"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
+      <c r="L76" s="37"/>
+      <c r="M76" s="37"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="qAAaSxdcCzritEHx0hkNzh7ZaZyVQqWmLOZaL5KHN1tPPyKYC4GBNwuEL6WsbdcGxo4oCjOfoWY6dgIuDdT6kA==" saltValue="uGmcMPPduR93sptcPrrfaA==" spinCount="100000" sqref="J2 L2" name="범위1"/>
+    <protectedRange algorithmName="SHA-512" hashValue="qAAaSxdcCzritEHx0hkNzh7ZaZyVQqWmLOZaL5KHN1tPPyKYC4GBNwuEL6WsbdcGxo4oCjOfoWY6dgIuDdT6kA==" saltValue="uGmcMPPduR93sptcPrrfaA==" spinCount="100000" sqref="J2:K2 M2" name="범위1"/>
   </protectedRanges>
-  <mergeCells count="142">
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="B75:L75"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="G63:L63"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="D65:L65"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B69:L69"/>
-    <mergeCell ref="B70:L70"/>
-    <mergeCell ref="B72:L72"/>
-    <mergeCell ref="B73:L73"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="B9:L9"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="B71:L71"/>
-    <mergeCell ref="B74:L74"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B76:L76"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L4:L5"/>
+  <mergeCells count="141">
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="B71:M71"/>
+    <mergeCell ref="B74:M74"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B76:M76"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="M4:M5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J7:M7"/>
     <mergeCell ref="C10:E10"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="L10:M10"/>
     <mergeCell ref="C12:E12"/>
-    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="L12:M12"/>
     <mergeCell ref="B3:J4"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="L13:M13"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="E8:H8"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="B75:M75"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="G63:M63"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="D65:M65"/>
+    <mergeCell ref="B67:M67"/>
+    <mergeCell ref="B69:M69"/>
+    <mergeCell ref="B70:M70"/>
+    <mergeCell ref="B72:M72"/>
+    <mergeCell ref="B73:M73"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="L55:M55"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="J2:L2">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="J2:M2">
       <formula1>"마지막 업데이트: 2025-02-07"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2596,88 +2696,88 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
     </row>
     <row r="3" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
     </row>
     <row r="4" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
     </row>
     <row r="5" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
     </row>
     <row r="6" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
     </row>
     <row r="8" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
     </row>
     <row r="9" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
     </row>
     <row r="10" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
     </row>
     <row r="11" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
     </row>
     <row r="12" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
     </row>
     <row r="13" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="12">
